--- a/templates/samples/SALES_ONBUY_SAMPLE.xlsx
+++ b/templates/samples/SALES_ONBUY_SAMPLE.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -495,28 +495,28 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-07-08</v>
+        <v>2026-07-09</v>
       </c>
       <c r="B3" t="str">
-        <v>ONB-5007</v>
+        <v>ONB-5008</v>
       </c>
       <c r="C3" t="str">
-        <v>GOO-128GB-WHI</v>
+        <v>IPH-64GB-PUR</v>
       </c>
       <c r="D3" t="str">
-        <v>350100000055433</v>
+        <v>350100000063352</v>
       </c>
       <c r="E3" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F3">
-        <v>260.29</v>
+        <v>196.74</v>
       </c>
       <c r="G3">
-        <v>329.11</v>
+        <v>251.83</v>
       </c>
       <c r="H3">
-        <v>68.82</v>
+        <v>55.09</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -528,7 +528,7 @@
         <v/>
       </c>
       <c r="L3">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -542,28 +542,28 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-07-12</v>
+        <v>2026-07-14</v>
       </c>
       <c r="B4" t="str">
-        <v>ONB-5011</v>
+        <v>ONB-5013</v>
       </c>
       <c r="C4" t="str">
-        <v>IPH-256GB-BLA</v>
+        <v>SAM-128GB-BLU</v>
       </c>
       <c r="D4" t="str">
-        <v>350100000087109</v>
+        <v>350100000102947</v>
       </c>
       <c r="E4" t="str">
         <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F4">
-        <v>514.23</v>
+        <v>230.57</v>
       </c>
       <c r="G4">
-        <v>660.92</v>
+        <v>310.06</v>
       </c>
       <c r="H4">
-        <v>146.68999999999994</v>
+        <v>79.49000000000001</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -589,28 +589,28 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-07-16</v>
+        <v>2026-07-19</v>
       </c>
       <c r="B5" t="str">
-        <v>ONB-5015</v>
+        <v>ONB-5018</v>
       </c>
       <c r="C5" t="str">
-        <v>GOO-128GB-BLA</v>
+        <v>IPH-128GB-BLU</v>
       </c>
       <c r="D5" t="str">
-        <v>350100000118785</v>
+        <v>350100000142542</v>
       </c>
       <c r="E5" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F5">
-        <v>280.37</v>
+        <v>316.37</v>
       </c>
       <c r="G5">
-        <v>418.03</v>
+        <v>409.99</v>
       </c>
       <c r="H5">
-        <v>137.65999999999997</v>
+        <v>93.62</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -622,7 +622,7 @@
         <v/>
       </c>
       <c r="L5">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -636,28 +636,28 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-07-20</v>
+        <v>2026-07-24</v>
       </c>
       <c r="B6" t="str">
-        <v>ONB-5019</v>
+        <v>ONB-5023</v>
       </c>
       <c r="C6" t="str">
-        <v>IPH-256GB-GRA</v>
+        <v>GOO-128GB-BLA</v>
       </c>
       <c r="D6" t="str">
-        <v>350100000150461</v>
+        <v>350100000182137</v>
       </c>
       <c r="E6" t="str">
         <v>CELLHUB TRADING</v>
       </c>
       <c r="F6">
-        <v>529.23</v>
+        <v>276.86</v>
       </c>
       <c r="G6">
-        <v>685.84</v>
+        <v>347.16</v>
       </c>
       <c r="H6">
-        <v>156.61</v>
+        <v>70.30000000000001</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -669,7 +669,7 @@
         <v/>
       </c>
       <c r="L6">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="M6" t="str">
         <v/>
@@ -683,28 +683,28 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-07-24</v>
+        <v>2026-07-05</v>
       </c>
       <c r="B7" t="str">
-        <v>ONB-5023</v>
+        <v>ONB-5028</v>
       </c>
       <c r="C7" t="str">
-        <v>GOO-128GB-BLA</v>
+        <v>IPH-256GB-GRA</v>
       </c>
       <c r="D7" t="str">
-        <v>350100000182137</v>
+        <v>350100000221732</v>
       </c>
       <c r="E7" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F7">
-        <v>276.86</v>
+        <v>499.6</v>
       </c>
       <c r="G7">
-        <v>386.46</v>
+        <v>644.6</v>
       </c>
       <c r="H7">
-        <v>109.59999999999997</v>
+        <v>145</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -716,7 +716,7 @@
         <v/>
       </c>
       <c r="L7">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="M7" t="str">
         <v/>
@@ -730,28 +730,28 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-10</v>
       </c>
       <c r="B8" t="str">
-        <v>ONB-5027</v>
+        <v>ONB-5033</v>
       </c>
       <c r="C8" t="str">
-        <v>IPH-256GB-MID</v>
+        <v>IPH-128GB-GRE</v>
       </c>
       <c r="D8" t="str">
-        <v>350100000213813</v>
+        <v>350100000261327</v>
       </c>
       <c r="E8" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F8">
-        <v>499.91</v>
+        <v>209.59</v>
       </c>
       <c r="G8">
-        <v>712.92</v>
+        <v>298.71</v>
       </c>
       <c r="H8">
-        <v>213.00999999999993</v>
+        <v>89.11999999999998</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -777,28 +777,28 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-07-08</v>
+        <v>2026-07-15</v>
       </c>
       <c r="B9" t="str">
-        <v>ONB-5031</v>
+        <v>ONB-5038</v>
       </c>
       <c r="C9" t="str">
-        <v>GOO-128GB-GRE</v>
+        <v>SAM-256GB-MID</v>
       </c>
       <c r="D9" t="str">
-        <v>350100000245489</v>
+        <v>350100000300922</v>
       </c>
       <c r="E9" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F9">
-        <v>290.37</v>
+        <v>422.16</v>
       </c>
       <c r="G9">
-        <v>388.18</v>
+        <v>534.52</v>
       </c>
       <c r="H9">
-        <v>97.81</v>
+        <v>112.35999999999996</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -824,28 +824,28 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-07-12</v>
+        <v>2026-07-20</v>
       </c>
       <c r="B10" t="str">
-        <v>ONB-5035</v>
+        <v>ONB-5043</v>
       </c>
       <c r="C10" t="str">
-        <v>IPH-256GB-GRE</v>
+        <v>IPH-256GB-STA</v>
       </c>
       <c r="D10" t="str">
-        <v>350100000277165</v>
+        <v>350100000340517</v>
       </c>
       <c r="E10" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F10">
-        <v>495.98</v>
+        <v>500.85</v>
       </c>
       <c r="G10">
-        <v>706.88</v>
+        <v>631.84</v>
       </c>
       <c r="H10">
-        <v>210.89999999999998</v>
+        <v>130.99</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v/>
       </c>
       <c r="L10">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -871,28 +871,28 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-07-16</v>
+        <v>2026-07-01</v>
       </c>
       <c r="B11" t="str">
-        <v>ONB-5039</v>
+        <v>ONB-5048</v>
       </c>
       <c r="C11" t="str">
-        <v>GOO-128GB-GRA</v>
+        <v>IPH-128GB-BLA</v>
       </c>
       <c r="D11" t="str">
-        <v>350100000308841</v>
+        <v>350100000388031</v>
       </c>
       <c r="E11" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F11">
-        <v>268.59</v>
+        <v>232.81</v>
       </c>
       <c r="G11">
-        <v>369.04</v>
+        <v>298.59</v>
       </c>
       <c r="H11">
-        <v>100.45000000000005</v>
+        <v>65.77999999999997</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -904,7 +904,7 @@
         <v/>
       </c>
       <c r="L11">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -918,28 +918,28 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-07-20</v>
+        <v>2026-07-06</v>
       </c>
       <c r="B12" t="str">
-        <v>ONB-5043</v>
+        <v>ONB-5053</v>
       </c>
       <c r="C12" t="str">
-        <v>IPH-256GB-STA</v>
+        <v>SAM-128GB-STA</v>
       </c>
       <c r="D12" t="str">
-        <v>350100000340517</v>
+        <v>350100000419707</v>
       </c>
       <c r="E12" t="str">
-        <v>NORTHSIDE STOCK</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F12">
-        <v>500.85</v>
+        <v>243.53</v>
       </c>
       <c r="G12">
-        <v>661.97</v>
+        <v>336.62</v>
       </c>
       <c r="H12">
-        <v>161.12</v>
+        <v>93.09</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -965,28 +965,28 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-07-24</v>
+        <v>2026-07-11</v>
       </c>
       <c r="B13" t="str">
-        <v>ONB-5047</v>
+        <v>ONB-5058</v>
       </c>
       <c r="C13" t="str">
-        <v>GOO-128GB-GRA</v>
+        <v>IPH-128GB-WHI</v>
       </c>
       <c r="D13" t="str">
-        <v>350100000372193</v>
+        <v>350100000459302</v>
       </c>
       <c r="E13" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F13">
-        <v>256.93</v>
+        <v>336.42</v>
       </c>
       <c r="G13">
-        <v>380.8</v>
+        <v>468.11</v>
       </c>
       <c r="H13">
-        <v>123.87</v>
+        <v>131.69</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -998,7 +998,7 @@
         <v/>
       </c>
       <c r="L13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M13" t="str">
         <v/>
@@ -1012,28 +1012,28 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-16</v>
       </c>
       <c r="B14" t="str">
-        <v>ONB-5051</v>
+        <v>ONB-5063</v>
       </c>
       <c r="C14" t="str">
-        <v>IPH-256GB-GRE</v>
+        <v>GOO-128GB-BLU</v>
       </c>
       <c r="D14" t="str">
-        <v>350100000403869</v>
+        <v>350100000498897</v>
       </c>
       <c r="E14" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F14">
-        <v>533.2</v>
+        <v>287.02</v>
       </c>
       <c r="G14">
-        <v>683.86</v>
+        <v>379.48</v>
       </c>
       <c r="H14">
-        <v>150.65999999999997</v>
+        <v>92.46000000000004</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -1045,7 +1045,7 @@
         <v/>
       </c>
       <c r="L14">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -1059,28 +1059,28 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-07-08</v>
+        <v>2026-07-21</v>
       </c>
       <c r="B15" t="str">
-        <v>ONB-5055</v>
+        <v>ONB-5068</v>
       </c>
       <c r="C15" t="str">
-        <v>GOO-128GB-MID</v>
+        <v>IPH-256GB-MID</v>
       </c>
       <c r="D15" t="str">
-        <v>350100000435545</v>
+        <v>350100000538492</v>
       </c>
       <c r="E15" t="str">
         <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F15">
-        <v>267</v>
+        <v>482.51</v>
       </c>
       <c r="G15">
-        <v>358.72</v>
+        <v>628.06</v>
       </c>
       <c r="H15">
-        <v>91.72000000000003</v>
+        <v>145.54999999999995</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -1092,7 +1092,7 @@
         <v/>
       </c>
       <c r="L15">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -1106,28 +1106,28 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-07-12</v>
+        <v>2026-07-02</v>
       </c>
       <c r="B16" t="str">
-        <v>ONB-5059</v>
+        <v>ONB-5073</v>
       </c>
       <c r="C16" t="str">
-        <v>IPH-256GB-BLA</v>
+        <v>IPH-128GB-MID</v>
       </c>
       <c r="D16" t="str">
-        <v>350100000467221</v>
+        <v>350100000578087</v>
       </c>
       <c r="E16" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F16">
-        <v>507.95</v>
+        <v>222.91</v>
       </c>
       <c r="G16">
-        <v>658.85</v>
+        <v>305.01</v>
       </c>
       <c r="H16">
-        <v>150.90000000000003</v>
+        <v>82.1</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -1153,28 +1153,28 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-07-16</v>
+        <v>2026-07-07</v>
       </c>
       <c r="B17" t="str">
-        <v>ONB-5063</v>
+        <v>ONB-5078</v>
       </c>
       <c r="C17" t="str">
-        <v>GOO-128GB-BLU</v>
+        <v>SAM-256GB-GRE</v>
       </c>
       <c r="D17" t="str">
-        <v>350100000498897</v>
+        <v>350100000617682</v>
       </c>
       <c r="E17" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>PHONEBOX DIRECT</v>
       </c>
       <c r="F17">
-        <v>287.02</v>
+        <v>422.7</v>
       </c>
       <c r="G17">
-        <v>373.16</v>
+        <v>601.22</v>
       </c>
       <c r="H17">
-        <v>86.14000000000004</v>
+        <v>178.52000000000004</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -1186,7 +1186,7 @@
         <v/>
       </c>
       <c r="L17">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M17" t="str">
         <v/>
@@ -1200,28 +1200,28 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-07-20</v>
+        <v>2026-07-12</v>
       </c>
       <c r="B18" t="str">
-        <v>ONB-5067</v>
+        <v>ONB-5083</v>
       </c>
       <c r="C18" t="str">
-        <v>IPH-256GB-GRA</v>
+        <v>IPH-256GB-PUR</v>
       </c>
       <c r="D18" t="str">
-        <v>350100000530573</v>
+        <v>350100000657277</v>
       </c>
       <c r="E18" t="str">
-        <v>CELLHUB TRADING</v>
+        <v>MOBILE WHOLESALE LTD</v>
       </c>
       <c r="F18">
-        <v>500.16</v>
+        <v>511.35</v>
       </c>
       <c r="G18">
-        <v>661.28</v>
+        <v>700.16</v>
       </c>
       <c r="H18">
-        <v>161.11999999999995</v>
+        <v>188.80999999999995</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -1233,7 +1233,7 @@
         <v/>
       </c>
       <c r="L18">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M18" t="str">
         <v/>
@@ -1247,28 +1247,28 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-07-24</v>
+        <v>2026-07-17</v>
       </c>
       <c r="B19" t="str">
-        <v>ONB-5071</v>
+        <v>ONB-5088</v>
       </c>
       <c r="C19" t="str">
-        <v>GOO-128GB-BLU</v>
+        <v>IPH-64GB-STA</v>
       </c>
       <c r="D19" t="str">
-        <v>350100000562249</v>
+        <v>350100000696872</v>
       </c>
       <c r="E19" t="str">
-        <v>PHONEBOX DIRECT</v>
+        <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F19">
-        <v>264.82</v>
+        <v>186.57</v>
       </c>
       <c r="G19">
-        <v>348.17</v>
+        <v>264.87</v>
       </c>
       <c r="H19">
-        <v>83.35000000000002</v>
+        <v>78.30000000000001</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -1280,7 +1280,7 @@
         <v/>
       </c>
       <c r="L19">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -1294,28 +1294,28 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-07-04</v>
+        <v>2026-07-22</v>
       </c>
       <c r="B20" t="str">
-        <v>ONB-5075</v>
+        <v>ONB-5093</v>
       </c>
       <c r="C20" t="str">
-        <v>IPH-256GB-BLA</v>
+        <v>SAM-128GB-MID</v>
       </c>
       <c r="D20" t="str">
-        <v>350100000593925</v>
+        <v>350100007863567</v>
       </c>
       <c r="E20" t="str">
         <v>NORTHSIDE STOCK</v>
       </c>
       <c r="F20">
-        <v>501.14</v>
+        <v>242</v>
       </c>
       <c r="G20">
-        <v>742.15</v>
+        <v>353.11</v>
       </c>
       <c r="H20">
-        <v>241.01</v>
+        <v>111.11000000000001</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1327,7 +1327,7 @@
         <v/>
       </c>
       <c r="L20">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="M20" t="str">
         <v/>
@@ -1341,28 +1341,28 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-07-08</v>
+        <v>2026-07-03</v>
       </c>
       <c r="B21" t="str">
-        <v>ONB-5079</v>
+        <v>ONB-5098</v>
       </c>
       <c r="C21" t="str">
-        <v>GOO-128GB-WHI</v>
+        <v>IPH-128GB-BLA</v>
       </c>
       <c r="D21" t="str">
-        <v>350100000625601</v>
+        <v>350100007903162</v>
       </c>
       <c r="E21" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
+        <v>CELLHUB TRADING</v>
       </c>
       <c r="F21">
-        <v>262.14</v>
+        <v>327.58</v>
       </c>
       <c r="G21">
-        <v>340.26</v>
+        <v>485.49</v>
       </c>
       <c r="H21">
-        <v>78.12</v>
+        <v>157.91000000000003</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1374,7 +1374,7 @@
         <v/>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M21" t="str">
         <v/>
@@ -1383,247 +1383,12 @@
         <v/>
       </c>
       <c r="O21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>2026-07-12</v>
-      </c>
-      <c r="B22" t="str">
-        <v>ONB-5083</v>
-      </c>
-      <c r="C22" t="str">
-        <v>IPH-256GB-PUR</v>
-      </c>
-      <c r="D22" t="str">
-        <v>350100000657277</v>
-      </c>
-      <c r="E22" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
-      </c>
-      <c r="F22">
-        <v>511.35</v>
-      </c>
-      <c r="G22">
-        <v>727.31</v>
-      </c>
-      <c r="H22">
-        <v>215.95999999999992</v>
-      </c>
-      <c r="I22" t="str">
-        <v/>
-      </c>
-      <c r="J22" t="str">
-        <v/>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22">
-        <v>2</v>
-      </c>
-      <c r="M22" t="str">
-        <v/>
-      </c>
-      <c r="N22" t="str">
-        <v/>
-      </c>
-      <c r="O22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>2026-07-16</v>
-      </c>
-      <c r="B23" t="str">
-        <v>ONB-5087</v>
-      </c>
-      <c r="C23" t="str">
-        <v>GOO-128GB-STA</v>
-      </c>
-      <c r="D23" t="str">
-        <v>350100000688953</v>
-      </c>
-      <c r="E23" t="str">
-        <v>PHONEBOX DIRECT</v>
-      </c>
-      <c r="F23">
-        <v>275.49</v>
-      </c>
-      <c r="G23">
-        <v>389.63</v>
-      </c>
-      <c r="H23">
-        <v>114.13999999999999</v>
-      </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
-      <c r="J23" t="str">
-        <v/>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23">
-        <v>8</v>
-      </c>
-      <c r="M23" t="str">
-        <v/>
-      </c>
-      <c r="N23" t="str">
-        <v/>
-      </c>
-      <c r="O23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>2026-07-20</v>
-      </c>
-      <c r="B24" t="str">
-        <v>ONB-5091</v>
-      </c>
-      <c r="C24" t="str">
-        <v>IPH-256GB-GRA</v>
-      </c>
-      <c r="D24" t="str">
-        <v>350100007847729</v>
-      </c>
-      <c r="E24" t="str">
-        <v>NORTHSIDE STOCK</v>
-      </c>
-      <c r="F24">
-        <v>530.25</v>
-      </c>
-      <c r="G24">
-        <v>719.58</v>
-      </c>
-      <c r="H24">
-        <v>189.33000000000004</v>
-      </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
-      <c r="J24" t="str">
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24">
-        <v>8</v>
-      </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <v/>
-      </c>
-      <c r="O24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>2026-07-24</v>
-      </c>
-      <c r="B25" t="str">
-        <v>ONB-5095</v>
-      </c>
-      <c r="C25" t="str">
-        <v>GOO-128GB-BLU</v>
-      </c>
-      <c r="D25" t="str">
-        <v>350100007879405</v>
-      </c>
-      <c r="E25" t="str">
-        <v>MOBILE WHOLESALE LTD</v>
-      </c>
-      <c r="F25">
-        <v>293.74</v>
-      </c>
-      <c r="G25">
-        <v>396.34</v>
-      </c>
-      <c r="H25">
-        <v>102.59999999999997</v>
-      </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
-      <c r="J25" t="str">
-        <v/>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25">
-        <v>8</v>
-      </c>
-      <c r="M25" t="str">
-        <v/>
-      </c>
-      <c r="N25" t="str">
-        <v/>
-      </c>
-      <c r="O25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>2026-07-04</v>
-      </c>
-      <c r="B26" t="str">
-        <v>ONB-5099</v>
-      </c>
-      <c r="C26" t="str">
-        <v>IPH-256GB-BLA</v>
-      </c>
-      <c r="D26" t="str">
-        <v>350100007911081</v>
-      </c>
-      <c r="E26" t="str">
-        <v>PHONEBOX DIRECT</v>
-      </c>
-      <c r="F26">
-        <v>517.1</v>
-      </c>
-      <c r="G26">
-        <v>754.52</v>
-      </c>
-      <c r="H26">
-        <v>237.41999999999996</v>
-      </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26">
-        <v>8</v>
-      </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
-      <c r="N26" t="str">
-        <v/>
-      </c>
-      <c r="O26" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O21"/>
   </ignoredErrors>
 </worksheet>
 </file>